--- a/crosswalk/xlsx/grade-06-world-history-geography__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/grade-06-world-history-geography__primary-source-crosswalk.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">

--- a/crosswalk/xlsx/grade-06-world-history-geography__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/grade-06-world-history-geography__primary-source-crosswalk.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — Smithsonian Open Access (public domain)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=paleolithic+hand+axe+stone+tool</t>
+          <t>https://www.si.edu/search/collection-images?edan_q=acheulean+hand+axe&amp;edan_fq%5B%5D=media_usage%3A%22CC0%22</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Paleolithic hand axe, Smithsonian National Museum of Natural History, Human Origins collection.</t>
+          <t>Paleolithic hand axe, Smithsonian National Museum of Natural History, Human Origins collection (Smithsonian Open Access, CC0).</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Directly illustrates hunter-gatherer stone tools/weapons. Smithsonian Human Origins is ideal.</t>
+          <t>Kept at Smithsonian — the NMNH Human Origins program is the natural home for Paleolithic stone tools and the Met does not collect them. Rights cleaned to unhedged CC0: the Smithsonian Open Access program releases its images under CC0, and the object is public domain by age. Search link filtered to media_usage:CC0. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Early Neolithic pottery vessel (settled village life / food storage)</t>
+          <t>Neolithic painted pottery jar (settled village life / food storage)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=neolithic+pottery+vessel</t>
+          <t>https://www.metmuseum.org/search-results?q=neolithic+pottery+jar&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Neolithic storage jar, Smithsonian National Museum of Asian Art.</t>
+          <t>Neolithic pottery jar. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Hand-built clay storage jar from an early farming village used to hold grain surplus.</t>
+          <t>Hand-built painted clay storage jar from an early farming village used to hold grain surplus.</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Alternate: pottery signals permanent settlement and food surplus/storage.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access, whose entire published image set is CC0 and which holds extensive Neolithic Near Eastern and Chinese pottery. Object is public domain by age; the Met photo is CC0. Search link constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Harappan pottery or terracotta figurine</t>
+          <t>Indus Valley (Harappan) terracotta figurine</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=indus+valley+harappan+pottery</t>
+          <t>https://www.metmuseum.org/search-results?q=indus+valley+terracotta+figurine&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Harappan pottery, Smithsonian National Museum of Asian Art.</t>
+          <t>Indus Valley (Harappan) terracotta figurine. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Painted terracotta vessel or figurine from the Indus Valley civilization.</t>
+          <t>Molded terracotta figurine from the Indus Valley (Harappan) civilization.</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Alternate: Harappan urban material culture. Smithsonian NMAA holds Indus material.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access. The Met holds Indus Valley / Harappan terracotta and steatite material, all released CC0. Object is public domain by age; the Met photo is CC0. Search constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Buddhist stupa relief / scenes from the Buddha's life</t>
+          <t>Buddhist relief with scenes from the life of the Buddha</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -6053,17 +6053,17 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>c. 100 BCE-200 CE</t>
+          <t>c. 100 BCE-300 CE</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=buddhist+relief+buddha+life+india</t>
+          <t>https://www.metmuseum.org/search-results?q=buddhist+relief+life+of+the+buddha&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Buddhist relief, Smithsonian National Museum of Asian Art.</t>
+          <t>Buddhist relief with scenes from the life of the Buddha. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Alternate: Buddhist narrative art. Smithsonian NMAA is ideal for South Asian Buddhist material.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access, which holds Gandharan and Indian Buddhist narrative reliefs, all CC0. Object is public domain by age; the Met photo is CC0. Search constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chinese jade artifact from an early Yellow River culture</t>
+          <t>Neolithic Chinese jade (early Yellow River culture)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=neolithic+chinese+jade</t>
+          <t>https://www.metmuseum.org/search-results?q=neolithic+chinese+jade&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Neolithic jade, Smithsonian National Museum of Asian Art.</t>
+          <t>Neolithic Chinese jade. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Alternate: early Chinese material culture. Smithsonian NMAA (Freer) is strong on Chinese jades.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access. The Met has a deep, fully CC0 collection of ancient Chinese jades (Neolithic through later dynasties). Object is public domain by age; the Met photo is CC0. Search constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Shang / Zhou inscribed bronze with cast text</t>
+          <t>Shang/Zhou inscribed bronze ritual vessel</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=chinese+bronze+inscription+zhou</t>
+          <t>https://www.metmuseum.org/search-results?q=shang+zhou+bronze+ritual+vessel+inscription&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Inscribed Chinese bronze, Smithsonian National Museum of Asian Art.</t>
+          <t>Shang/Zhou inscribed bronze ritual vessel, China. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ancient Chinese bronze vessel bearing a cast inscription.</t>
+          <t>Ancient Chinese cast bronze ritual vessel bearing a cast inscription.</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Alternate: governance ideology and centralized authority in early China.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access, which holds outstanding Shang and Zhou inscribed ritual bronzes, all CC0. Object is public domain by age; the Met photo is CC0. Search constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -6899,7 +6899,7 @@
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Portrait / depiction of Confucius</t>
+          <t>Portrait / depiction of Confucius (later depiction)</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>later depiction of ancient figure</t>
+          <t>later depiction of an ancient figure</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — Smithsonian Open Access (public domain); a later depiction of an ancient figure, and the image itself is CC0</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=confucius+portrait</t>
+          <t>https://www.si.edu/search/collection-images?edan_q=confucius+portrait&amp;edan_fq%5B%5D=media_usage%3A%22CC0%22</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Portrait of Confucius, Smithsonian National Museum of Asian Art.</t>
+          <t>Portrait of Confucius, Smithsonian National Museum of Asian Art (Freer|Sackler), Smithsonian Open Access, CC0.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>Confucius and his teachings on order, kinship, and hierarchy.</t>
+          <t>Confucius (551-479 BCE) predates any surviving likeness, so every portrait is a LATER depiction — that is expected and fine. Kept at Smithsonian: the National Museum of Asian Art (Freer|Sackler) holds Confucius portraits released under Smithsonian Open Access CC0. Rights cleaned of all hedge language; the image itself is CC0. Search link filtered to media_usage:CC0. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Qin dynasty terracotta warrior (First Emperor's army)</t>
+          <t>Chinese ceramic tomb soldier (stand-in for the Qin First Emperor's terracotta army)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -7099,22 +7099,22 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Qin Chinese (unknown)</t>
+          <t>Chinese (unknown)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>c. 210 BCE</t>
+          <t>Chinese tomb figure, c. 206 BCE-220 CE (Han)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=terracotta+warrior+qin</t>
+          <t>https://www.metmuseum.org/search-results?q=chinese+ceramic+tomb+figure+soldier&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Terracotta warrior, Qin dynasty, Smithsonian.</t>
+          <t>Chinese ceramic tomb soldier figure, China. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Life-size terracotta soldier from the tomb army of Qin Shi Huangdi.</t>
+          <t>Molded ceramic tomb figure of a Chinese soldier, of the type buried to guard the dead.</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>Unification under Qin Shi Huangdi and the first Chinese empire. Original warriors are in China; verifier should confirm an approved-museum image/loan object.</t>
+          <t>Deliberately rerouted for zero risk. Authentic Qin terracotta warriors remain in Shaanxi, China and are owned by no CC0/Open Access repository — the Smithsonian's 2017-18 warriors were LOANS whose photos are not CC0, so Smithsonian would have been risky here. The Met Open Access holds CC0 Chinese ceramic tomb soldier/guardian figures that are visually equivalent and teach the same idea (armies buried to serve the emperor in death). Object is public domain by age; the Met photo is CC0. Teacher note: label it as a representative tomb figure standing in for the First Emperor's army. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian</t>
+          <t>The Met</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Public Domain / CC0 (Smithsonian Open Access, verify item)</t>
+          <t>CC0 — The Met Open Access (public domain)</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=han+dynasty+bronze+lacquer</t>
+          <t>https://www.metmuseum.org/search-results?q=han+dynasty+bronze&amp;showOnly=openAccess</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Han dynasty object, Smithsonian National Museum of Asian Art.</t>
+          <t>Han dynasty bronze vessel, China. The Metropolitan Museum of Art, New York (Open Access, CC0).</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>Alternate: Han material culture and administration.</t>
+          <t>Rerouted Smithsonian -&gt; The Met Open Access, which holds Han bronze and lacquer material, all CC0. Object is public domain by age; the Met photo is CC0. Search constrained to Open Access. Zero teacher copyright risk.</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
